--- a/Generators/Experiment with utility data leak/diffusion_dataleak/7. CDC diabetes dataset/TRTR_TSTR_results.xlsx
+++ b/Generators/Experiment with utility data leak/diffusion_dataleak/7. CDC diabetes dataset/TRTR_TSTR_results.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,102 +502,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
     </row>
@@ -612,353 +608,353 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
     </row>
@@ -969,47 +965,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
     </row>
@@ -1182,224 +1178,224 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.8594328795314231</v>
+        <v>0.865</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001759943124097367</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2332054266594181</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02311148836982272</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4856082623037368</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01937159125545948</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1538985939497231</v>
+        <v>0.865</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01868074662662275</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8594 ± 0.0018</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2332 ± 0.0231</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4856 ± 0.0194</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1539 ± 0.0187</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.005952192496438302</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.06091212454596739</v>
+        <v>0.07770850231074355</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1156112213063848</v>
+        <v>0.1367473263768655</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05333049282772336</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8458979737217034</v>
+        <v>0.8625</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002917769493011457</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2957141512829655</v>
+        <v>0.8011379217986173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01191860841862675</v>
+        <v>0.001766402176797399</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4073866373875522</v>
+        <v>0.7479310027409777</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01658665615007694</v>
+        <v>0.0004163356235445011</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2322965487856838</v>
+        <v>0.8625</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01168656640890678</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8459 ± 0.0029</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2957 ± 0.0119</t>
+          <t>0.8011 ± 0.0018</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4074 ± 0.0166</t>
+          <t>0.7479 ± 0.0004</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.2323 ± 0.0117</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.01856696216558484</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.03177654511158778</v>
+        <v>0.06021963775504025</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1371948670745904</v>
+        <v>0.139646074232981</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05681011219997162</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -1410,780 +1406,780 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8604875732151337</v>
+        <v>0.865</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001281887740118282</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1989911005639252</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01500809222967246</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4982550661193003</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0187804029255209</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1246129811106377</v>
+        <v>0.865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01208270422522765</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8605 ± 0.0013</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1990 ± 0.0150</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.4983 ± 0.0188</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1246 ± 0.0121</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.003102738641760361</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.07718616409934326</v>
+        <v>0.03713364422670384</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0928409769750092</v>
+        <v>0.1445197421022294</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.05671069450362165</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.856987098306158</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001738656117874269</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2715592523047302</v>
+        <v>0.8016366389712081</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01050519745940829</v>
+        <v>0.001686805320122046</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4680979723508488</v>
+        <v>0.7480483645500228</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01428075603395597</v>
+        <v>0.0003977256889716439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1914642806419543</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01030959740478241</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8570 ± 0.0017</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2716 ± 0.0105</t>
+          <t>0.8016 ± 0.0017</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0143</t>
+          <t>0.7480 ± 0.0004</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.1915 ± 0.0103</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.006559680227956277</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.03269013578241131</v>
+        <v>0.04441301317189239</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06787068852641004</v>
+        <v>0.1169626266931032</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0377787246129811</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.852685214500554</v>
+        <v>0.8445</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004990014161301725</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3054179008255341</v>
+        <v>0.796119240811636</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04469072687172702</v>
+        <v>0.008756581182760924</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4471802147018231</v>
+        <v>0.758487229663299</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03475350145014876</v>
+        <v>0.01834829525959637</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2357619656298821</v>
+        <v>0.8445</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05021098864555093</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.8527 ± 0.0050</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3054 ± 0.0447</t>
+          <t>0.7961 ± 0.0088</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.4472 ± 0.0348</t>
+          <t>0.7585 ± 0.0183</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2358 ± 0.0502</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.01043612474275757</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0146854099958777</v>
+        <v>0.04932449630506364</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0757594314131807</v>
+        <v>0.1023404936343565</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.03422809260048287</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.8582060313439925</v>
+        <v>0.8535</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009257278421097861</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2026390078200694</v>
+        <v>0.7965978908265624</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01406088839275979</v>
+        <v>0.005845409311343877</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4680956246527622</v>
+        <v>0.7468518093699863</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01129415337352562</v>
+        <v>0.001392603248407127</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1295128532878853</v>
+        <v>0.8535</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01107295433695692</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.8582 ± 0.0009</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2026 ± 0.0141</t>
+          <t>0.7966 ± 0.0058</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0113</t>
+          <t>0.7469 ± 0.0014</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.1295 ± 0.0111</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003700332436282761</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05165139419108342</v>
+        <v>0.03889636800971263</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01112718599970741</v>
+        <v>0.1001880623640177</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04355915352932818</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.7933453379768878</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008179284861907412</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3083582846944011</v>
+        <v>0.7879238545634504</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01201275374419538</v>
+        <v>0.007710276594733493</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2895576392844975</v>
+        <v>0.7495954822625809</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008417614778537561</v>
+        <v>0.01130598131083171</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3313733844624343</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02846916497887783</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.7933 ± 0.0082</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.3084 ± 0.0120</t>
+          <t>0.7879 ± 0.0077</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.2896 ± 0.0084</t>
+          <t>0.7496 ± 0.0113</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.3314 ± 0.0285</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.0643580813677378</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.05654729225266808</v>
+        <v>0.06136772251082456</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1814670725776874</v>
+        <v>0.09357302407311441</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1594091748331203</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.8530750356181732</v>
+        <v>0.8455</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001212077950855918</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1982972877374191</v>
+        <v>0.795035527912038</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01733491557879429</v>
+        <v>0.008164230429254637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4129480942886304</v>
+        <v>0.7569794205256127</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01702310751314772</v>
+        <v>0.01940062770836523</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1306632580599347</v>
+        <v>0.8455</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01363324333261546</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.8531 ± 0.0012</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.1983 ± 0.0173</t>
+          <t>0.7950 ± 0.0082</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.4129 ± 0.0170</t>
+          <t>0.7570 ± 0.0194</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.1307 ± 0.0136</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.001739354123793113</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05052936704710131</v>
+        <v>0.01704222904517638</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.007419739977004791</v>
+        <v>0.03782804105365167</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.04608720352222695</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.8443703498496122</v>
+        <v>0.7595</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002155324629646412</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="P10" t="n">
-        <v>0.231243963132944</v>
+        <v>0.7579048370761177</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0137006705544126</v>
+        <v>0.0287833643353949</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3707827247491188</v>
+        <v>0.7580658653685093</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01709342485110321</v>
+        <v>0.01422434066153863</v>
       </c>
       <c r="T10" t="n">
-        <v>0.168115324527766</v>
+        <v>0.7595</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01152280256385812</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.8444 ± 0.0022</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.2312 ± 0.0137</t>
+          <t>0.7579 ± 0.0288</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3708 ± 0.0171</t>
+          <t>0.7581 ± 0.0142</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.1681 ± 0.0115</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.002845496279879622</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04476334007692173</v>
+        <v>0.04125039486402204</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03544963348478625</v>
+        <v>0.04886106433443871</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04093168584007956</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -2194,332 +2190,332 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.2876800696533165</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01325794881831392</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2721032847164263</v>
+        <v>0.7584484002038779</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.003645391628123934</v>
+        <v>0.005896346373562807</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1586495092299866</v>
+        <v>0.7597922138141208</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002465782440245203</v>
+        <v>0.005570077145047665</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9553756568669224</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005611274864304836</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.2877 ± 0.0133</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.2721 ± 0.0036</t>
+          <t>0.7584 ± 0.0059</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.1586 ± 0.0025</t>
+          <t>0.7598 ± 0.0056</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.9554 ± 0.0056</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.4852619914516383</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1390282087054183</v>
+        <v>0.0111169111686189</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1632314142795934</v>
+        <v>0.09325531141598231</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.3864649907683568</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.8555406047174292</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00377696765177999</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="P12" t="n">
-        <v>0.009733384613800168</v>
+        <v>0.8740589613153219</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.006780845959806028</v>
+        <v>0.008504514563610215</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1303637540525382</v>
+        <v>0.8717974753920386</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0703114812688721</v>
+        <v>0.009961185756881206</v>
       </c>
       <c r="T12" t="n">
-        <v>0.005169720210197415</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.003746991905084153</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.8555 ± 0.0038</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.0097 ± 0.0068</t>
+          <t>0.8741 ± 0.0085</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.1304 ± 0.0703</t>
+          <t>0.8718 ± 0.0100</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.0052 ± 0.0037</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>0.009844467310432203</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1625599174996505</v>
+        <v>0.006035599976654926</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.4708557295575835</v>
+        <v>0.01317485098482685</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.09539838091180228</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.8481953458920373</v>
+        <v>0.892</v>
       </c>
       <c r="O13" t="n">
-        <v>0.00515717857077356</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="P13" t="n">
-        <v>0.03961698089772425</v>
+        <v>0.8748453500252168</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01568461328391349</v>
+        <v>0.007458169753921906</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1702923936811873</v>
+        <v>0.8792862472502394</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02442399879718625</v>
+        <v>0.01186372439962882</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02289447521658855</v>
+        <v>0.892</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01039500870734086</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.8482 ± 0.0052</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.0396 ± 0.0157</t>
+          <t>0.8748 ± 0.0075</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.1703 ± 0.0244</t>
+          <t>0.8793 ± 0.0119</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0.0229 ± 0.0104</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>0.01626958999525097</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.2243206252736535</v>
+        <v>-0.01348779047155924</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3742891107809553</v>
+        <v>0.008290829723719306</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.1525919613691237</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -2530,780 +2526,780 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D14" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.8606735792306475</v>
+        <v>0.89</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.8622741608593515</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.0107043530784709</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.8831176570216487</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.01004847749414569</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.8607 ± 0.0000</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8623 ± 0.0107</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8831 ± 0.0100</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>0.002916732626246588</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.121804936464582</v>
+        <v>-0.02275445765141437</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.009627085080580633</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.06790228660701605</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E15" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.8601393066328953</v>
+        <v>0.867</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0005102049190908339</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="P15" t="n">
-        <v>0.001013054635224362</v>
+        <v>0.8317730476364493</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001075337642532265</v>
+        <v>0.009232178771023704</v>
       </c>
       <c r="R15" t="n">
-        <v>0.08009597637504615</v>
+        <v>0.8361931687425281</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05699063662778444</v>
+        <v>0.02217992328586535</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0005112910097997443</v>
+        <v>0.867</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0005434207206280071</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.8601 ± 0.0005</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.0010 ± 0.0011</t>
+          <t>0.8318 ± 0.0092</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.0801 ± 0.0570</t>
+          <t>0.8362 ± 0.0222</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.0005 ± 0.0005</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>0.003407471901219039</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.2378560618870945</v>
+        <v>0.01427660450665114</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4558726845022126</v>
+        <v>0.02881782250059783</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1531742650191734</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G16" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.8605687034984962</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0001207060313439867</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003115709756448731</v>
+        <v>0.8356806037864141</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0004643040521165739</v>
+        <v>0.01296409706277128</v>
       </c>
       <c r="R16" t="n">
-        <v>0.08583333333333334</v>
+        <v>0.8278647307416687</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1153527199505933</v>
+        <v>0.01624445982897337</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0001562278085499219</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0002329387795321222</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.8606 ± 0.0001</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.0003 ± 0.0005</t>
+          <t>0.8357 ± 0.0130</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.0858 ± 0.1154</t>
+          <t>0.8279 ± 0.0162</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0.0002 ± 0.0002</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.002552635744815346</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.2904209198540115</v>
+        <v>0.009763133330285556</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4371063127816704</v>
+        <v>0.03296299255598678</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2013776452208493</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E17" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.8585087858160518</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="O17" t="n">
-        <v>0.000923277687889107</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="P17" t="n">
-        <v>0.00294689508052617</v>
+        <v>0.8390546705140765</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.001366092119697046</v>
+        <v>0.01296203029878578</v>
       </c>
       <c r="R17" t="n">
-        <v>0.08194104491453391</v>
+        <v>0.8446664360507107</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01995972588599695</v>
+        <v>0.01936142229675867</v>
       </c>
       <c r="T17" t="n">
-        <v>0.001505467973299247</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0007106942765628066</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.8585 ± 0.0009</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.0029 ± 0.0014</t>
+          <t>0.8391 ± 0.0130</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.0819 ± 0.0200</t>
+          <t>0.8447 ± 0.0194</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.0015 ± 0.0007</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>6.727877156897932e-05</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2513435069306267</v>
+        <v>-0.003560411677801412</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3972817657379357</v>
+        <v>0.00237343568329329</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.1715665388439142</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C18" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H18" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I18" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.7278692417286687</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0.02918620347758178</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1496721451029945</v>
+        <v>0.8513079585760513</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02576138707150587</v>
+        <v>0.01472495814796158</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1333702775690188</v>
+        <v>0.8452658116236673</v>
       </c>
       <c r="S18" t="n">
-        <v>0.018098328120112</v>
+        <v>0.01704866229207197</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1745916773185627</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0448853839259956</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.7279 ± 0.0292</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.1497 ± 0.0258</t>
+          <t>0.8513 ± 0.0147</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.1334 ± 0.0181</t>
+          <t>0.8453 ± 0.0170</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.1746 ± 0.0449</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>0.1298341776159568</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.1021388473387386</v>
+        <v>-0.00201638150177641</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.3376544342931661</v>
+        <v>-0.002097305287972029</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.00262746768924868</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.8518679753047333</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>0.001281820538095891</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="P19" t="n">
-        <v>0.01348859401639657</v>
+        <v>0.8397690328049215</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.003660832807467163</v>
+        <v>0.008733820353619547</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0927921871297462</v>
+        <v>0.8344313125015056</v>
       </c>
       <c r="S19" t="n">
-        <v>0.01738189120774628</v>
+        <v>0.01128806302708654</v>
       </c>
       <c r="T19" t="n">
-        <v>0.007285896889646357</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.002043437308587493</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.8519 ± 0.0013</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.0135 ± 0.0037</t>
+          <t>0.8398 ± 0.0087</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.0928 ± 0.0174</t>
+          <t>0.8344 ± 0.0113</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.0073 ± 0.0020</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>-0.000532293810353246</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.2353380607681239</v>
+        <v>-0.02769127584770714</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.327575647135889</v>
+        <v>-0.03962385092224119</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1694645646925153</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E20" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I20" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.8458029919265474</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.001758857064936351</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="P20" t="n">
-        <v>0.02865520606143544</v>
+        <v>0.7869109458280485</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.004073347901818477</v>
+        <v>0.02195959925702665</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1172782293793152</v>
+        <v>0.81003273111726</v>
       </c>
       <c r="S20" t="n">
-        <v>0.01220490747916881</v>
+        <v>0.0191996780030147</v>
       </c>
       <c r="T20" t="n">
-        <v>0.01634710978554182</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.002488848681350422</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.8458 ± 0.0018</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.0287 ± 0.0041</t>
+          <t>0.7869 ± 0.0220</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.1173 ± 0.0122</t>
+          <t>0.8100 ± 0.0192</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.0163 ± 0.0025</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>0.001412854202944458</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.2473520971484303</v>
+        <v>0.01224428611209116</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.2889541288545898</v>
+        <v>-0.003105801414312048</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1926999005823037</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -3314,108 +3310,108 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F21" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G21" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I21" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.8468933037834414</v>
+        <v>0.5515</v>
       </c>
       <c r="O21" t="n">
-        <v>0.02330599669903018</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="P21" t="n">
-        <v>0.003204708991913499</v>
+        <v>0.5707855242882436</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.004453870499127896</v>
+        <v>0.2617419349196998</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2309094898784584</v>
+        <v>0.864237257200078</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3871458237319818</v>
+        <v>0.01629017285189378</v>
       </c>
       <c r="T21" t="n">
-        <v>0.002130379207498935</v>
+        <v>0.5515</v>
       </c>
       <c r="U21" t="n">
-        <v>0.003106427635731815</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.8469 ± 0.0233</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.0032 ± 0.0045</t>
+          <t>0.5708 ± 0.2617</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.2309 ± 0.3871</t>
+          <t>0.8642 ± 0.0163</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.0021 ± 0.0031</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>-0.07395124267848663</v>
+        <v>0.2065</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.4079267844299311</v>
+        <v>0.1987797870842533</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.09097143363112159</v>
+        <v>-0.01118973196997497</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.5667802868910666</v>
+        <v>0.2065</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -3467,16 +3463,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.009182167167959453</v>
+        <v>0.02165</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2281061757594843</v>
+        <v>0.04384729193677982</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3771657290369433</v>
+        <v>0.1013921766280741</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1768328362448516</v>
+        <v>0.02165</v>
       </c>
     </row>
     <row r="3">
@@ -3486,16 +3482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.05957139464935882</v>
+        <v>0.02539999999999996</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001217463823266921</v>
+        <v>0.01715890938596775</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08879722316143546</v>
+        <v>0.003923032693450445</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06541542394546231</v>
+        <v>0.02539999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -3509,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3661,6 +3657,1126 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.01106797181058934</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8800945612919768</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.01557076241163555</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8849723263768654</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01637849998720951</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8965</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.01106797181058934</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.8965 ± 0.0111</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.8801 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.8850 ± 0.0164</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.8965 ± 0.0111</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8023860589812333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.7482249999999999</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.1702778228589e-16</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.8650 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.8024 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.7482 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.8650 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.03149999999999997</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.07770850231074355</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1367473263768655</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.03149999999999997</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.004972144630058771</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.8613575595536576</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00835629357808527</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8875770769739587</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.009319454743331457</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8905</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.004972144630058771</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.8905 ± 0.0050</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.8614 ± 0.0084</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.8876 ± 0.0093</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.8905 ± 0.0050</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.003535533905932741</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8011379217986173</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.001766402176797399</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.7479310027409777</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.0004163356235445011</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.003535533905932741</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.8625 ± 0.0035</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.8011 ± 0.0018</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.7479 ± 0.0004</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.8625 ± 0.0035</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.02799999999999991</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.06021963775504025</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.139646074232981</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.02799999999999991</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.004116363011742827</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8395197032079371</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.007183950573405901</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8927447421022293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01169636211175201</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.004116363011742827</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.8815 ± 0.0041</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.8395 ± 0.0072</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.8927 ± 0.0117</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.8815 ± 0.0041</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8023860589812333</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.7482249999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.1702778228589e-16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.8650 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.8024 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.7482 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.8650 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.01649999999999996</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.03713364422670384</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1445197421022294</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.01649999999999996</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.008164965809277268</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8460496521431005</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.01294479429530151</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.865010991243126</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02161817607890089</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8800000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.008164965809277268</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.8800 ± 0.0082</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.8460 ± 0.0129</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.8650 ± 0.0216</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.8800 ± 0.0082</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8634999999999999</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.003374742788552767</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8016366389712081</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.001686805320122046</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.7480483645500228</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.0003977256889716439</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8634999999999999</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.003374742788552767</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.8635 ± 0.0034</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.8016 ± 0.0017</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.7480 ± 0.0004</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.8635 ± 0.0034</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.01650000000000018</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04441301317189239</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1169626266931032</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.01650000000000018</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8775000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.008249579113843062</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8454437371166996</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.009700800200490399</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8608277232976554</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02216917078425409</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8775000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.008249579113843062</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.8775 ± 0.0082</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.8454 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8608 ± 0.0222</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.8775 ± 0.0082</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8445</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01802005056103403</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.796119240811636</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.008756581182760924</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.758487229663299</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.01834829525959637</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8445</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.01802005056103403</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.8445 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.7961 ± 0.0088</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.7585 ± 0.0183</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.8445 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.03300000000000003</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04932449630506364</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1023404936343565</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.03300000000000003</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8724999999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.007168604389202195</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.835494258836275</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01145355069185408</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.847039871734004</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01822934405953743</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8724999999999999</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.007168604389202195</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.8725 ± 0.0072</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.8355 ± 0.0115</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8470 ± 0.0182</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8725 ± 0.0072</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.01155902725626648</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.7965978908265624</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.005845409311343877</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.7468518093699863</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.001392603248407127</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01155902725626648</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.8535 ± 0.0116</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.7966 ± 0.0058</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.7469 ± 0.0014</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.8535 ± 0.0116</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.01899999999999991</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.03889636800971263</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1001880623640177</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.01899999999999991</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.008834905520465721</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8492915770742749</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.01093808385599739</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8431685063356953</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01341255506478664</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.8665</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.008834905520465721</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.8665 ± 0.0088</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.8493 ± 0.0109</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8432 ± 0.0134</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.8665 ± 0.0088</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.8324999999999999</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01317615691736823</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7879238545634504</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.007710276594733493</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.7495954822625809</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.01130598131083171</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8324999999999999</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.01317615691736823</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.8325 ± 0.0132</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.7879 ± 0.0077</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.7496 ± 0.0113</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.8325 ± 0.0132</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.03400000000000014</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.06136772251082456</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.09357302407311441</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.03400000000000014</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.8484999999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.008514693182963209</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.8120777569572144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.009746337201211541</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7948074615792644</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01564230257413808</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.8484999999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.008514693182963209</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.8485 ± 0.0085</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8121 ± 0.0097</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.7948 ± 0.0156</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.8485 ± 0.0085</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01039497741967513</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.795035527912038</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.008164230429254637</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.7569794205256127</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01940062770836523</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.8455</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01039497741967513</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.8455 ± 0.0104</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.7950 ± 0.0082</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.7570 ± 0.0194</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.8455 ± 0.0104</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.002999999999999892</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.01704222904517638</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.03782804105365167</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.002999999999999892</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.02786873995477129</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7991552319401397</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01874904662857105</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.806926929702948</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01474411983059894</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.02786873995477129</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.7940 ± 0.0279</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.7992 ± 0.0187</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.8069 ± 0.0147</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.7940 ± 0.0279</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04969071006402169</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7579048370761177</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.0287833643353949</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.7580658653685093</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01422434066153863</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.7595</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.04969071006402169</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.7595 ± 0.0497</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.7579 ± 0.0288</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.7581 ± 0.0142</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.7595 ± 0.0497</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.03450000000000009</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.04125039486402204</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.04886106433443871</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.03450000000000009</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1786710198474653</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7695653113724968</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1866093154578636</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8530475252301031</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01193960102018576</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1786710198474653</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.7580 ± 0.1787</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.7696 ± 0.1866</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.8530 ± 0.0119</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.7580 ± 0.1787</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7575000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01359125535858342</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7584484002038779</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.005896346373562807</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.7597922138141208</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.005570077145047665</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7575000000000001</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01359125535858342</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.7575 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.7584 ± 0.0059</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.7598 ± 0.0056</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.7575 ± 0.0136</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.0004999999999999449</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.0111169111686189</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.09325531141598231</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.0004999999999999449</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -3675,504 +4791,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4331,108 +4949,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.8594328795314231</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001759943124097367</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2332054266594181</v>
+        <v>0.8740589613153219</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02311148836982272</v>
+        <v>0.008504514563610215</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4856082623037368</v>
+        <v>0.8717974753920386</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01937159125545948</v>
+        <v>0.009961185756881206</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1538985939497231</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01868074662662275</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8594 ± 0.0018</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2332 ± 0.0231</t>
+          <t>0.8741 ± 0.0085</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4856 ± 0.0194</t>
+          <t>0.8718 ± 0.0100</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1539 ± 0.0187</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.005952192496438302</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.06091212454596739</v>
+        <v>0.006035599976654926</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1156112213063848</v>
+        <v>0.01317485098482685</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05333049282772336</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -4443,108 +5061,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8458979737217034</v>
+        <v>0.892</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002917769493011457</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2957141512829655</v>
+        <v>0.8748453500252168</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01191860841862675</v>
+        <v>0.007458169753921906</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4073866373875522</v>
+        <v>0.8792862472502394</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01658665615007694</v>
+        <v>0.01186372439962882</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2322965487856838</v>
+        <v>0.892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01168656640890678</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8459 ± 0.0029</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2957 ± 0.0119</t>
+          <t>0.8748 ± 0.0075</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4074 ± 0.0166</t>
+          <t>0.8793 ± 0.0119</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.2323 ± 0.0117</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.01856696216558484</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.03177654511158778</v>
+        <v>-0.01348779047155924</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1371948670745904</v>
+        <v>0.008290829723719306</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05681011219997162</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -4559,104 +5177,104 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8604875732151337</v>
+        <v>0.89</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001281887740118282</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1989911005639252</v>
+        <v>0.8622741608593515</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01500809222967246</v>
+        <v>0.0107043530784709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4982550661193003</v>
+        <v>0.8831176570216487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0187804029255209</v>
+        <v>0.01004847749414569</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1246129811106377</v>
+        <v>0.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01208270422522765</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8605 ± 0.0013</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1990 ± 0.0150</t>
+          <t>0.8623 ± 0.0107</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.4983 ± 0.0188</t>
+          <t>0.8831 ± 0.0100</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1246 ± 0.0121</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.003102738641760361</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.07718616409934326</v>
+        <v>-0.02275445765141437</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0928409769750092</v>
+        <v>0.009627085080580633</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.05671069450362165</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -4667,108 +5285,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.856987098306158</v>
+        <v>0.867</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001738656117874269</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2715592523047302</v>
+        <v>0.8317730476364493</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01050519745940829</v>
+        <v>0.009232178771023704</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4680979723508488</v>
+        <v>0.8361931687425281</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01428075603395597</v>
+        <v>0.02217992328586535</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1914642806419543</v>
+        <v>0.867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01030959740478241</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8570 ± 0.0017</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2716 ± 0.0105</t>
+          <t>0.8318 ± 0.0092</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0143</t>
+          <t>0.8362 ± 0.0222</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.1915 ± 0.0103</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.006559680227956277</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.03269013578241131</v>
+        <v>0.01427660450665114</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06787068852641004</v>
+        <v>0.02881782250059783</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0377787246129811</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -4779,108 +5397,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.852685214500554</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004990014161301725</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3054179008255341</v>
+        <v>0.8356806037864141</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04469072687172702</v>
+        <v>0.01296409706277128</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4471802147018231</v>
+        <v>0.8278647307416687</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03475350145014876</v>
+        <v>0.01624445982897337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2357619656298821</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05021098864555093</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.8527 ± 0.0050</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3054 ± 0.0447</t>
+          <t>0.8357 ± 0.0130</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.4472 ± 0.0348</t>
+          <t>0.8279 ± 0.0162</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2358 ± 0.0502</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.01043612474275757</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0146854099958777</v>
+        <v>0.009763133330285556</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0757594314131807</v>
+        <v>0.03296299255598678</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.03422809260048287</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -4891,108 +5509,108 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.8582060313439925</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009257278421097861</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2026390078200694</v>
+        <v>0.8390546705140765</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01406088839275979</v>
+        <v>0.01296203029878578</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4680956246527622</v>
+        <v>0.8446664360507107</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01129415337352562</v>
+        <v>0.01936142229675867</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1295128532878853</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01107295433695692</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.8582 ± 0.0009</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2026 ± 0.0141</t>
+          <t>0.8391 ± 0.0130</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0113</t>
+          <t>0.8447 ± 0.0194</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.1295 ± 0.0111</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003700332436282761</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05165139419108342</v>
+        <v>-0.003560411677801412</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01112718599970741</v>
+        <v>0.00237343568329329</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04355915352932818</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -5003,108 +5621,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.7933453379768878</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008179284861907412</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3083582846944011</v>
+        <v>0.8513079585760513</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01201275374419538</v>
+        <v>0.01472495814796158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2895576392844975</v>
+        <v>0.8452658116236673</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008417614778537561</v>
+        <v>0.01704866229207197</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3313733844624343</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02846916497887783</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.7933 ± 0.0082</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.3084 ± 0.0120</t>
+          <t>0.8513 ± 0.0147</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.2896 ± 0.0084</t>
+          <t>0.8453 ± 0.0170</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.3314 ± 0.0285</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.0643580813677378</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.05654729225266808</v>
+        <v>-0.00201638150177641</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1814670725776874</v>
+        <v>-0.002097305287972029</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1594091748331203</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -5115,108 +5733,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.8530750356181732</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001212077950855918</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1982972877374191</v>
+        <v>0.8397690328049215</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01733491557879429</v>
+        <v>0.008733820353619547</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4129480942886304</v>
+        <v>0.8344313125015056</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01702310751314772</v>
+        <v>0.01128806302708654</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1306632580599347</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01363324333261546</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.8531 ± 0.0012</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.1983 ± 0.0173</t>
+          <t>0.8398 ± 0.0087</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.4129 ± 0.0170</t>
+          <t>0.8344 ± 0.0113</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.1307 ± 0.0136</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.001739354123793113</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05052936704710131</v>
+        <v>-0.02769127584770714</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.007419739977004791</v>
+        <v>-0.03962385092224119</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.04608720352222695</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -5227,108 +5845,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.8443703498496122</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002155324629646412</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="P10" t="n">
-        <v>0.231243963132944</v>
+        <v>0.7869109458280485</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0137006705544126</v>
+        <v>0.02195959925702665</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3707827247491188</v>
+        <v>0.81003273111726</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01709342485110321</v>
+        <v>0.0191996780030147</v>
       </c>
       <c r="T10" t="n">
-        <v>0.168115324527766</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01152280256385812</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.8444 ± 0.0022</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.2312 ± 0.0137</t>
+          <t>0.7869 ± 0.0220</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3708 ± 0.0171</t>
+          <t>0.8100 ± 0.0192</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.1681 ± 0.0115</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.002845496279879622</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04476334007692173</v>
+        <v>0.01224428611209116</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03544963348478625</v>
+        <v>-0.003105801414312048</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04093168584007956</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -5343,1394 +5961,108 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.2876800696533165</v>
+        <v>0.5515</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01325794881831392</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2721032847164263</v>
+        <v>0.5707855242882436</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.003645391628123934</v>
+        <v>0.2617419349196998</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1586495092299866</v>
+        <v>0.864237257200078</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002465782440245203</v>
+        <v>0.01629017285189378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9553756568669224</v>
+        <v>0.5515</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005611274864304836</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.2877 ± 0.0133</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.2721 ± 0.0036</t>
+          <t>0.5708 ± 0.2617</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.1586 ± 0.0025</t>
+          <t>0.8642 ± 0.0163</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.9554 ± 0.0056</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.4852619914516383</v>
+        <v>0.2065</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1390282087054183</v>
+        <v>0.1987797870842533</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1632314142795934</v>
+        <v>-0.01118973196997497</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.3864649907683568</v>
+        <v>0.2065</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>ForestDiffusion</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>GradientBoost</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.8653850720278614</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1722933021134507</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.004133046767167164</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.6012194836101217</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.01161315896115709</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.1005681011219997</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.002743294672201886</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.8654 ± 0.0005</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.1723 ± 0.0041</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0.6012 ± 0.0116</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.1006 ± 0.0027</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.8555406047174292</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.00377696765177999</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.009733384613800168</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.006780845959806028</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.1303637540525382</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.0703114812688721</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.005169720210197415</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.003746991905084153</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.8555 ± 0.0038</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.0097 ± 0.0068</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.1304 ± 0.0703</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.0052 ± 0.0037</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.009844467310432203</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.1625599174996505</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.4708557295575835</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.09539838091180228</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8644649358872882</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.001292019377334109</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.2639376061713777</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.0296521977876718</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5445815044621426</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.01990884968502404</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.1754864365857122</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.02609605447626427</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.8645 ± 0.0013</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.2639 ± 0.0297</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.5446 ± 0.0199</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.1755 ± 0.0261</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.8481953458920373</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.00515717857077356</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.03961698089772425</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.01568461328391349</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1702923936811873</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.02442399879718625</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.02289447521658855</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.01039500870734086</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.8482 ± 0.0052</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.0396 ± 0.0157</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.1703 ± 0.0244</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.0229 ± 0.0104</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.01626958999525097</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.2243206252736535</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.3742891107809553</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.1525919613691237</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SVM-RBF</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.8635903118568941</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.121804936464582</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.00369981836688605</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5910960430943095</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.01145382697210849</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.06790228660701605</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.002191473549437678</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.8636 ± 0.0004</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.1218 ± 0.0037</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.5911 ± 0.0115</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.0679 ± 0.0022</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8606735792306475</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.8607 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.002916732626246588</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.121804936464582</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.5910960430943095</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.06790228660701605</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>LogReg</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8635467785341143</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2388691165223189</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.004564487931064464</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5359686608772588</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.00934558839892455</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.1536855560289732</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.003128072545874311</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.8635 ± 0.0007</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.2389 ± 0.0046</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.5360 ± 0.0093</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.1537 ± 0.0031</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0.8601393066328953</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.0005102049190908339</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.001013054635224362</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.001075337642532265</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.08009597637504615</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.05699063662778444</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.0005112910097997443</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.0005434207206280071</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.8601 ± 0.0005</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.0010 ± 0.0011</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.0801 ± 0.0570</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.0005 ± 0.0005</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.003407471901219039</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.2378560618870945</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.4558726845022126</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.1531742650191734</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AdaBoost</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.8631213392433116</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.2907324908296564</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.01155213366104772</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5229396461150038</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.006564777307101441</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.2015338730293992</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.01144868243932203</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.8631 ± 0.0006</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.2907 ± 0.0116</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.5229 ± 0.0066</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.2015 ± 0.0114</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.8605687034984962</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.0001207060313439867</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.0003115709756448731</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.0004643040521165739</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.08583333333333334</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1153527199505933</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.0001562278085499219</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.0002329387795321222</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.8606 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.0003 ± 0.0005</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.0858 ± 0.1154</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.0002 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.002552635744815346</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.2904209198540115</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.4371063127816704</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.2013776452208493</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8585760645876208</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.2542904020111528</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.004123268112439032</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.4792228106524696</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.0086336230115462</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.1730720068172134</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.003012275509749968</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.8586 ± 0.0009</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.2543 ± 0.0041</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.4792 ± 0.0086</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.1731 ± 0.0030</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0.8585087858160518</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.000923277687889107</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.00294689508052617</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.001366092119697046</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.08194104491453391</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.01995972588599695</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.001505467973299247</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.0007106942765628066</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.8585 ± 0.0009</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.0029 ± 0.0014</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.0819 ± 0.0200</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.0015 ± 0.0007</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.727877156897932e-05</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.2513435069306267</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.3972817657379357</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.1715665388439142</v>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8577034193446256</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.001100478021426305</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.2518109924417331</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.00902185699517897</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4710247118621849</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.01001864628250197</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.171964209629314</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.008237907025316163</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.8577 ± 0.0011</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.2518 ± 0.0090</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.4710 ± 0.0100</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.1720 ± 0.0082</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0.7278692417286687</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.02918620347758178</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.1496721451029945</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.02576138707150587</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1333702775690188</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.018098328120112</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.1745916773185627</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.0448853839259956</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.7279 ± 0.0292</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.1497 ± 0.0258</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0.1334 ± 0.0181</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.1746 ± 0.0449</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.1298341776159568</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.1021388473387386</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.3376544342931661</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>-0.00262746768924868</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ExtraTrees</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.8513356814943801</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.2488266547845204</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.00511286061119995</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.4203678342656352</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.006991258369007768</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1767504615821616</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.00462847729159016</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.8513 ± 0.0009</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.2488 ± 0.0051</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.4204 ± 0.0070</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.1768 ± 0.0046</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>0.8518679753047333</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.001281820538095891</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.01348859401639657</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.003660832807467163</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.0927921871297462</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.01738189120774628</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.007285896889646357</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.002043437308587493</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.8519 ± 0.0013</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.0135 ± 0.0037</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.0928 ± 0.0174</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.0073 ± 0.0020</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
-        <v>-0.000532293810353246</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.2353380607681239</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.327575647135889</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.1694645646925153</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.8472158461294919</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.2760073032098657</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.003654438442907095</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.4062323582339051</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.00489709142841155</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.2090470103678455</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.004094394489595194</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.8472 ± 0.0009</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.2760 ± 0.0037</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.4062 ± 0.0049</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.2090 ± 0.0041</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0.8458029919265474</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.001758857064936351</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.02865520606143544</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.004073347901818477</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1172782293793152</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.01220490747916881</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.01634710978554182</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.002488848681350422</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.8458 ± 0.0018</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.0287 ± 0.0041</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.1173 ± 0.0122</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.0163 ± 0.0025</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.001412854202944458</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.2473520971484303</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.2889541288545898</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.1926999005823037</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.7729420611049548</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.001604092504916999</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.4111314934218446</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.002269244542275589</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.32188092350958</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.001866083751005921</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5689106660985656</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.005812999479801975</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.7729 ± 0.0016</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.4111 ± 0.0023</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.3219 ± 0.0019</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.5689 ± 0.0058</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0.8468933037834414</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.02330599669903018</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.003204708991913499</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.004453870499127896</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.2309094898784584</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.3871458237319818</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.002130379207498935</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.003106427635731815</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.8469 ± 0.0233</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.0032 ± 0.0045</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.2309 ± 0.3871</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.0021 ± 0.0031</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>-0.07395124267848663</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0.4079267844299311</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.09097143363112159</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0.5667802868910666</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
         </is>
       </c>
     </row>
